--- a/GroupForms.xlsx
+++ b/GroupForms.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gpsiee\Documents\Courses\CET-CPET-563 Embedded Systems Design Capstone\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tjeff\Documents\ESD_Capstone_Tennis_Ball_Tracker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301A80FC-989C-4DE9-BBBA-DF9537F7F596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35193440-1D61-4884-B1B6-68A59F1BF9D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{CBBACBFF-7C6F-4024-89F0-E17BFE59D8AD}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CBBACBFF-7C6F-4024-89F0-E17BFE59D8AD}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
